--- a/data/2025/37-timis/155243-timisoara/budget_file.xlsx
+++ b/data/2025/37-timis/155243-timisoara/budget_file.xlsx
@@ -19443,7 +19443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19489,12 +19489,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -19502,54 +19502,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>03.00.01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 11.02 total: still inconsistent — UNRESOLVED</t>
+          <t>code 03.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>05.00.01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 30.02 total: still inconsistent — UNRESOLVED</t>
+          <t>code 05.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19558,41 +19548,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 42.02 total: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -19602,7 +19587,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 42.02 total: still inconsistent — UNRESOLVED</t>
+          <t>11.02 total: parent 273.271.680,00 != sum(children) 335.077.690,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -19618,66 +19603,66 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>03.00.01</t>
+          <t>18.00.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>code 03.00.01 (revenue) not in nomenclator</t>
+          <t>code 18.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>05.00.01</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>code 05.00.01 (revenue) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.02.01</t>
+          <t>30.00.02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
+          <t>code 30.00.02 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -19693,11 +19678,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -19707,7 +19692,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11.02 total: parent 273.271.680,00 != sum(children) 335.077.690,00 (1 children)</t>
+          <t>30.02 total: parent 21.749.240,00 != sum(children) 57.617.930,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -19727,12 +19712,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18.00.01</t>
+          <t>33.00.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>code 18.00.01 (revenue) not in nomenclator</t>
+          <t>code 33.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -19748,23 +19733,23 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30.02.01</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -19773,16 +19758,21 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30.00.02</t>
+          <t>42.02</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>code 30.00.02 (revenue) not in nomenclator</t>
+          <t>42.02 total: parent 772.044.940,00 != sum(children) 777.044.940,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -19798,11 +19788,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -19812,39 +19802,39 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30.02 total: parent 21.749.240,00 != sum(children) 57.617.930,00 (1 children)</t>
+          <t>51.02 total: parent 148.833.670,00 != sum(children) 24.448.350,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>33.00.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>code 33.00.01 (revenue) not in nomenclator</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -19853,46 +19843,41 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>42.02 total: parent 772.044.940,00 != sum(children) 777.044.940,00 (1 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
@@ -19908,11 +19893,11 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -19922,7 +19907,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.02 total: parent 148.833.670,00 != sum(children) 24.448.350,00 (1 children)</t>
+          <t>61.02 total: parent 46.583.220,00 != sum(children) 2.079.600,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -19938,7 +19923,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -19954,25 +19939,30 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>65.02 total: parent 451.250.430,00 != sum(children) 37.563.050,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19978,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -20017,7 +20007,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -20027,7 +20017,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.02 total: parent 46.583.220,00 != sum(children) 2.079.600,00 (1 children)</t>
+          <t>66.02 total: parent 78.088.720,00 != sum(children) 10.955.060,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -20068,11 +20058,11 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -20082,7 +20072,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>65.02 total: parent 451.250.430,00 != sum(children) 37.563.050,00 (1 children)</t>
+          <t>67.02 total: parent 282.282.580,00 != sum(children) 69.925.090,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -20098,7 +20088,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -20123,11 +20113,11 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -20137,7 +20127,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>66.02 total: parent 78.088.720,00 != sum(children) 10.955.060,00 (2 children)</t>
+          <t>68.02 total: parent 186.114.030,00 != sum(children) 1.554.720,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20143,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -20169,7 +20159,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -20180,11 +20170,6 @@
       <c r="C27" t="n">
         <v>6</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>total</t>
@@ -20192,32 +20177,37 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>67.02 total: parent 282.282.580,00 != sum(children) 69.925.090,00 (1 children)</t>
+          <t>unparseable cell '8.614.320 2.473.110' in column total</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>70.02 total: parent 212.093.120,00 != sum(children) 87.808.180,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -20233,11 +20223,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -20247,7 +20237,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>68.02 total: parent 186.114.030,00 != sum(children) 1.554.720,00 (2 children)</t>
+          <t>74.02 total: parent 175.363.680,00 != sum(children) 36.183.500,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -20263,16 +20253,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>duplicate of p3 with different values</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -20282,52 +20272,47 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>8</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>unparseable cell '8.614.320 2.473.110' in column total</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.02 total: parent 212.093.120,00 != sum(children) 87.808.180,00 (2 children)</t>
+          <t>duplicate of p7 with different values</t>
         </is>
       </c>
     </row>
@@ -20343,11 +20328,11 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -20357,19 +20342,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>74.02 total: parent 175.363.680,00 != sum(children) 36.183.500,00 (1 children)</t>
+          <t>84.02 total: parent 657.306.370,00 != sum(children) 140.075.090,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -20377,24 +20362,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>03.00.01</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>code 03.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -20402,19 +20387,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>05.00.01</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>code 05.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -20423,103 +20408,98 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>duplicate of p7 with different values</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>84.02 total: parent 657.306.370,00 != sum(children) 140.075.090,00 (1 children)</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>03.00.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>code 03.00.01 (revenue) not in nomenclator</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>05.00.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>code 05.00.01 (revenue) not in nomenclator</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -20528,16 +20508,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
@@ -20553,7 +20533,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -20603,7 +20583,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -20628,7 +20608,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -20644,25 +20624,30 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>70.02 total: parent 108.148.090,00 != sum(children) 57.425.250,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -20678,7 +20663,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -20703,7 +20688,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -20728,7 +20713,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -20744,62 +20729,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.02 total: parent 108.148.090,00 != sum(children) 57.425.250,00 (1 children)</t>
+          <t>duplicate of p10 with different values</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>99.02</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>99.02 total: parent 0,00 != sum(children) 57.425.250,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -20812,24 +20797,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -20837,12 +20822,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>33.00.01</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>code 33.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -20852,84 +20837,84 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>warning</t>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>13</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>01</t>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>duplicate of p10 with different values</t>
+          <t>unparseable cell '126.960 125.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>99.02</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>99.02 total: parent 0,00 != sum(children) 57.425.250,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>30.02.01</t>
+          <t>42.02</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
+          <t>42.02 total: parent 751.137.320,00 != sum(children) 756.137.320,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -20938,16 +20923,21 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>33.00.01</t>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>code 33.00.01 (revenue) not in nomenclator</t>
+          <t>65.02 total: parent 252.857.350,00 != sum(children) 38.763.050,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -20957,29 +20947,29 @@
           <t>V7_hygiene</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>13</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>15</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>01</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>unparseable cell '126.960 125.000' in column total</t>
+          <t>duplicate of p14 with different values</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -20988,101 +20978,96 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>42.02 total: parent 751.137.320,00 != sum(children) 756.137.320,00 (1 children)</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>65.02 total: parent 252.857.350,00 != sum(children) 38.763.050,00 (2 children)</t>
+          <t>duplicate of p15 with different values</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>duplicate of p14 with different values</t>
+          <t>67.02 total: parent 105.762.130,00 != sum(children) 69.925.090,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -21102,24 +21087,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>duplicate of p15 with different values</t>
+          <t>duplicate of p14 with different values</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -21127,12 +21112,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>duplicate of p15 with different values</t>
+          <t>68.02 total: parent 9.817.030,00 != sum(children) 1.554.720,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -21152,12 +21142,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>duplicate of p15 with different values</t>
+          <t>duplicate of p14 with different values</t>
         </is>
       </c>
     </row>
@@ -21173,11 +21163,11 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21187,7 +21177,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>67.02 total: parent 105.762.130,00 != sum(children) 69.925.090,00 (1 children)</t>
+          <t>70.02 total: parent 103.945.030,00 != sum(children) 30.382.930,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -21203,7 +21193,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -21228,11 +21218,11 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21242,7 +21232,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>68.02 total: parent 9.817.030,00 != sum(children) 1.554.720,00 (2 children)</t>
+          <t>74.02 total: parent 97.575.210,00 != sum(children) 36.183.500,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -21258,7 +21248,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -21287,7 +21277,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21297,7 +21287,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>70.02 total: parent 103.945.030,00 != sum(children) 30.382.930,00 (1 children)</t>
+          <t>81.02 total: parent 81.318.000,00 != sum(children) 1.318.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -21342,7 +21332,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21352,7 +21342,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>74.02 total: parent 97.575.210,00 != sum(children) 36.183.500,00 (1 children)</t>
+          <t>84.02 total: parent 478.869.690,00 != sum(children) 140.075.090,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -21393,11 +21383,11 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21406,116 +21396,6 @@
         </is>
       </c>
       <c r="F73" t="inlineStr">
-        <is>
-          <t>81.02 total: parent 81.318.000,00 != sum(children) 1.318.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>17</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>duplicate of p14 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>17</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>84.02 total: parent 478.869.690,00 != sum(children) 140.075.090,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>17</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>duplicate of p14 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>18</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>99.02</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
         <is>
           <t>99.02 total: parent 118.081.960,00 != sum(children) 354.485.390,00 (2 children)</t>
         </is>
@@ -21532,7 +21412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -21554,7 +21434,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -21564,60 +21444,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>346</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>276</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ff3a80264042003cf541a990</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cc5da585b570f3ff9e4024a2d1bd7155d93e488245969ae64fee733afc1f16d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>— Anexa (de la pagina 1)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-18, 649 linii</t>
         </is>
